--- a/output/pdf_financials_xlsx/SAF.H.xlsx
+++ b/output/pdf_financials_xlsx/SAF.H.xlsx
@@ -1288,28 +1288,28 @@
         <v>-0.275825</v>
       </c>
       <c r="K16" s="3" t="n">
-        <v>0.265249</v>
+        <v>-0.265249</v>
       </c>
       <c r="L16" s="3" t="n">
-        <v>1.545174</v>
+        <v>-1.545174</v>
       </c>
       <c r="M16" s="3" t="n">
-        <v>0.873107</v>
+        <v>-0.873107</v>
       </c>
       <c r="N16" s="3" t="n">
-        <v>0.667695</v>
+        <v>-0.667695</v>
       </c>
       <c r="O16" s="3" t="n">
-        <v>1.152524</v>
+        <v>-1.152524</v>
       </c>
       <c r="P16" s="3" t="n">
-        <v>0.675164</v>
+        <v>-0.675164</v>
       </c>
       <c r="Q16" s="3" t="n">
-        <v>5.356134</v>
+        <v>-5.356134</v>
       </c>
       <c r="R16" s="3" t="n">
-        <v>0.224603</v>
+        <v>-0.224603</v>
       </c>
     </row>
     <row r="17">
@@ -1588,28 +1588,28 @@
         <v>-0.275825</v>
       </c>
       <c r="K20" s="3" t="n">
-        <v>0.265249</v>
+        <v>-0.265249</v>
       </c>
       <c r="L20" s="3" t="n">
-        <v>1.545174</v>
+        <v>-1.545174</v>
       </c>
       <c r="M20" s="3" t="n">
-        <v>0.873107</v>
+        <v>-0.873107</v>
       </c>
       <c r="N20" s="3" t="n">
-        <v>0.667695</v>
+        <v>-0.667695</v>
       </c>
       <c r="O20" s="3" t="n">
-        <v>1.152524</v>
+        <v>-1.152524</v>
       </c>
       <c r="P20" s="3" t="n">
-        <v>0.675164</v>
+        <v>-0.675164</v>
       </c>
       <c r="Q20" s="3" t="n">
-        <v>5.356134</v>
+        <v>-5.356134</v>
       </c>
       <c r="R20" s="3" t="n">
-        <v>0.224603</v>
+        <v>-0.224603</v>
       </c>
     </row>
     <row r="21">
@@ -1762,28 +1762,28 @@
         <v>-0.275825</v>
       </c>
       <c r="K23" s="3" t="n">
-        <v>0.265249</v>
+        <v>-0.265249</v>
       </c>
       <c r="L23" s="3" t="n">
-        <v>1.545174</v>
+        <v>-1.545174</v>
       </c>
       <c r="M23" s="3" t="n">
-        <v>0.873107</v>
+        <v>-0.873107</v>
       </c>
       <c r="N23" s="3" t="n">
-        <v>0.667695</v>
+        <v>-0.667695</v>
       </c>
       <c r="O23" s="3" t="n">
-        <v>1.152524</v>
+        <v>-1.152524</v>
       </c>
       <c r="P23" s="3" t="n">
-        <v>0.675164</v>
+        <v>-0.675164</v>
       </c>
       <c r="Q23" s="3" t="n">
-        <v>5.356134</v>
+        <v>-5.356134</v>
       </c>
       <c r="R23" s="3" t="n">
-        <v>0.224603</v>
+        <v>-0.224603</v>
       </c>
     </row>
     <row r="24">
@@ -1987,7 +1987,7 @@
         </is>
       </c>
       <c r="L26" s="3" t="n">
-        <v>-38.62935</v>
+        <v>38.62935</v>
       </c>
       <c r="M26" s="1" t="inlineStr">
         <is>
@@ -2010,7 +2010,7 @@
         </is>
       </c>
       <c r="Q26" s="3" t="n">
-        <v>133.90335</v>
+        <v>-133.90335</v>
       </c>
       <c r="R26" s="1" t="inlineStr">
         <is>
@@ -2052,28 +2052,28 @@
         <v>-0.275988</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>0.265249</v>
+        <v>-0.265249</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>1.545174</v>
+        <v>-1.545174</v>
       </c>
       <c r="M27" s="3" t="n">
-        <v>0.873107</v>
+        <v>-0.873107</v>
       </c>
       <c r="N27" s="3" t="n">
-        <v>0.667695</v>
+        <v>-0.667695</v>
       </c>
       <c r="O27" s="3" t="n">
-        <v>1.152524</v>
+        <v>-1.152524</v>
       </c>
       <c r="P27" s="3" t="n">
-        <v>0.675164</v>
+        <v>-0.675164</v>
       </c>
       <c r="Q27" s="3" t="n">
-        <v>5.356134</v>
+        <v>-5.356134</v>
       </c>
       <c r="R27" s="3" t="n">
-        <v>0.224603</v>
+        <v>-0.224603</v>
       </c>
     </row>
     <row r="28">
@@ -2168,28 +2168,28 @@
         <v>-0.275988</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>0.265249</v>
+        <v>-0.265249</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>1.545174</v>
+        <v>-1.545174</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>0.873107</v>
+        <v>-0.873107</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>0.667695</v>
+        <v>-0.667695</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>1.152524</v>
+        <v>-1.152524</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>0.675164</v>
+        <v>-0.675164</v>
       </c>
       <c r="Q29" s="3" t="n">
-        <v>5.356134</v>
+        <v>-5.356134</v>
       </c>
       <c r="R29" s="3" t="n">
-        <v>0.224603</v>
+        <v>-0.224603</v>
       </c>
     </row>
     <row r="30">
@@ -2318,28 +2318,28 @@
         <v>-0</v>
       </c>
       <c r="K31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="L31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="M31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="N31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="O31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="P31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Q31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="R31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="32">
@@ -31920,10 +31920,10 @@
         </is>
       </c>
       <c r="T236" s="5" t="n">
-        <v>5.356134</v>
+        <v>-5.356134</v>
       </c>
       <c r="U236" s="5" t="n">
-        <v>0.224603</v>
+        <v>-0.224603</v>
       </c>
     </row>
     <row r="237">
@@ -33709,10 +33709,10 @@
         </is>
       </c>
       <c r="S254" s="5" t="n">
-        <v>0.675164</v>
+        <v>-0.675164</v>
       </c>
       <c r="T254" s="5" t="n">
-        <v>5.356134</v>
+        <v>-5.356134</v>
       </c>
       <c r="U254" t="inlineStr">
         <is>
@@ -35101,13 +35101,13 @@
         </is>
       </c>
       <c r="Q268" s="5" t="n">
-        <v>0.667695</v>
+        <v>-0.667695</v>
       </c>
       <c r="R268" s="5" t="n">
-        <v>1.152524</v>
+        <v>-1.152524</v>
       </c>
       <c r="S268" s="5" t="n">
-        <v>0.675164</v>
+        <v>-0.675164</v>
       </c>
       <c r="T268" t="inlineStr">
         <is>
@@ -38818,10 +38818,10 @@
         </is>
       </c>
       <c r="O305" s="5" t="n">
-        <v>1.545174</v>
+        <v>-1.545174</v>
       </c>
       <c r="P305" s="5" t="n">
-        <v>0.873107</v>
+        <v>-0.873107</v>
       </c>
       <c r="Q305" t="inlineStr">
         <is>
@@ -39926,10 +39926,10 @@
         </is>
       </c>
       <c r="N316" s="5" t="n">
-        <v>0.265249</v>
+        <v>-0.265249</v>
       </c>
       <c r="O316" s="5" t="n">
-        <v>1.545174</v>
+        <v>-1.545174</v>
       </c>
       <c r="P316" t="inlineStr">
         <is>

--- a/output/pdf_financials_xlsx/SAF.H.xlsx
+++ b/output/pdf_financials_xlsx/SAF.H.xlsx
@@ -1029,7 +1029,7 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>0.0007649999999999999</v>
       </c>
       <c r="C12" s="3" t="n">
         <v>0</v>
@@ -2025,7 +2025,7 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-0.268678</v>
+        <v>-0.269443</v>
       </c>
       <c r="C27" s="3" t="n">
         <v>-0.406074</v>
@@ -2141,7 +2141,7 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-0.268678</v>
+        <v>-0.269443</v>
       </c>
       <c r="C29" s="3" t="n">
         <v>-0.406074</v>
@@ -2448,7 +2448,7 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.000108</v>
       </c>
       <c r="C34" s="3" t="n">
         <v>0.004992</v>
@@ -2457,22 +2457,22 @@
         <v>0.030655</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.383336</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>0.256402</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>0.122784</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>0.250033</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>0.126192</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>0.09204900000000001</v>
       </c>
       <c r="K34" s="3" t="n">
         <v>0.436923</v>
@@ -2493,10 +2493,10 @@
         <v>0.045656</v>
       </c>
       <c r="Q34" s="3" t="n">
-        <v>0</v>
+        <v>0.067375</v>
       </c>
       <c r="R34" s="3" t="n">
-        <v>0</v>
+        <v>0.052444</v>
       </c>
     </row>
     <row r="35">
@@ -2564,7 +2564,7 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.000108</v>
       </c>
       <c r="C36" s="3" t="n">
         <v>0.004992</v>
@@ -2573,22 +2573,22 @@
         <v>0.030655</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>0.383336</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>0.256402</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>0.122784</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>0.250033</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>0.126192</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>0.09204900000000001</v>
       </c>
       <c r="K36" s="3" t="n">
         <v>0.436923</v>
@@ -2609,10 +2609,10 @@
         <v>0.045656</v>
       </c>
       <c r="Q36" s="3" t="n">
-        <v>0</v>
+        <v>0.067375</v>
       </c>
       <c r="R36" s="3" t="n">
-        <v>0</v>
+        <v>0.052444</v>
       </c>
     </row>
     <row r="37">
@@ -3269,7 +3269,7 @@
         <v>0.023857</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>0.38959</v>
+        <v>0.006254</v>
       </c>
       <c r="F48" s="3" t="n">
         <v>0</v>
@@ -3305,7 +3305,7 @@
         <v>0.01012</v>
       </c>
       <c r="Q48" s="3" t="n">
-        <v>0.079361</v>
+        <v>0.011986</v>
       </c>
       <c r="R48" s="3" t="n">
         <v>0</v>
@@ -8732,7 +8732,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -17158,7 +17158,7 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E89" s="5" t="n">
@@ -44421,7 +44421,7 @@
       </c>
       <c r="D362" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E362" t="inlineStr">
@@ -48800,7 +48800,7 @@
       </c>
       <c r="D405" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E405" s="5" t="n">

--- a/output/pdf_financials_xlsx/SAF.H.xlsx
+++ b/output/pdf_financials_xlsx/SAF.H.xlsx
@@ -739,10 +739,10 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>0.096641</v>
+        <v>0.126641</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>0.121448</v>
+        <v>0.154748</v>
       </c>
       <c r="D7" s="3" t="n">
         <v>0.063802</v>
@@ -913,10 +913,10 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>0.156691</v>
+        <v>0.186691</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>0.155514</v>
+        <v>0.188814</v>
       </c>
       <c r="D10" s="3" t="n">
         <v>0.283661</v>
@@ -3564,10 +3564,10 @@
         </is>
       </c>
       <c r="B53" s="3" t="n">
-        <v>0</v>
+        <v>0.000792</v>
       </c>
       <c r="C53" s="3" t="n">
-        <v>0</v>
+        <v>0.00063</v>
       </c>
       <c r="D53" s="3" t="n">
         <v>0</v>
@@ -4372,10 +4372,10 @@
         </is>
       </c>
       <c r="B66" s="3" t="n">
-        <v>0</v>
+        <v>0.074915</v>
       </c>
       <c r="C66" s="3" t="n">
-        <v>0</v>
+        <v>0.010866</v>
       </c>
       <c r="D66" s="3" t="n">
         <v>0.04485</v>
@@ -5710,10 +5710,10 @@
         </is>
       </c>
       <c r="B88" s="3" t="n">
-        <v>0</v>
+        <v>5.168187</v>
       </c>
       <c r="C88" s="3" t="n">
-        <v>0</v>
+        <v>5.916637</v>
       </c>
       <c r="D88" s="3" t="n">
         <v>6.110937</v>
@@ -5942,10 +5942,10 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>0</v>
+        <v>0.5768450000000001</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>0.744577</v>
       </c>
       <c r="D92" s="3" t="n">
         <v>0.744577</v>
@@ -16265,7 +16265,11 @@
           <t>Equipment – Note 3</t>
         </is>
       </c>
-      <c r="D80" t="inlineStr"/>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>MachineryFurnitureEquipment</t>
+        </is>
+      </c>
       <c r="E80" s="5" t="n">
         <v>0.000792</v>
       </c>
@@ -16364,7 +16368,11 @@
           <t>Mineral properties – Note 4</t>
         </is>
       </c>
-      <c r="D81" t="inlineStr"/>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>MineralProperties</t>
+        </is>
+      </c>
       <c r="E81" s="5" t="n">
         <v>1e-06</v>
       </c>
@@ -16564,7 +16572,11 @@
           <t>Due to related parties – Note 7</t>
         </is>
       </c>
-      <c r="D83" t="inlineStr"/>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>OtherPayable</t>
+        </is>
+      </c>
       <c r="E83" s="5" t="n">
         <v>0.074915</v>
       </c>
@@ -16760,7 +16772,11 @@
           <t>Share capital – Note 5</t>
         </is>
       </c>
-      <c r="D85" t="inlineStr"/>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>CapitalStock</t>
+        </is>
+      </c>
       <c r="E85" s="5" t="n">
         <v>5.168187</v>
       </c>
@@ -16857,7 +16873,11 @@
           <t>Contributed surplus- Note 5</t>
         </is>
       </c>
-      <c r="D86" t="inlineStr"/>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E86" s="5" t="n">
         <v>0.5768450000000001</v>
       </c>
@@ -45433,7 +45453,11 @@
           <t>Consulting fees – Note 7</t>
         </is>
       </c>
-      <c r="D372" t="inlineStr"/>
+      <c r="D372" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E372" t="inlineStr">
         <is>
           <t>-</t>
@@ -47772,7 +47796,11 @@
           <t>Consulting fees – Note 7</t>
         </is>
       </c>
-      <c r="D395" t="inlineStr"/>
+      <c r="D395" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E395" s="5" t="n">
         <v>0.03</v>
       </c>

--- a/output/pdf_financials_xlsx/SAF.H.xlsx
+++ b/output/pdf_financials_xlsx/SAF.H.xlsx
@@ -6423,28 +6423,28 @@
         </is>
       </c>
       <c r="B101" s="3" t="n">
-        <v>0</v>
+        <v>0.008094</v>
       </c>
       <c r="C101" s="3" t="n">
-        <v>0</v>
+        <v>0.007932</v>
       </c>
       <c r="D101" s="3" t="n">
-        <v>0</v>
+        <v>-0.01791</v>
       </c>
       <c r="E101" s="3" t="n">
-        <v>0</v>
+        <v>0.017197</v>
       </c>
       <c r="F101" s="3" t="n">
-        <v>0</v>
+        <v>0.002378</v>
       </c>
       <c r="G101" s="3" t="n">
-        <v>0</v>
+        <v>0.00158</v>
       </c>
       <c r="H101" s="3" t="n">
-        <v>0</v>
+        <v>-2.2e-05</v>
       </c>
       <c r="I101" s="3" t="n">
-        <v>0</v>
+        <v>-0.000393</v>
       </c>
       <c r="J101" s="3" t="n">
         <v>-0.00016</v>
@@ -6713,10 +6713,10 @@
         </is>
       </c>
       <c r="B106" s="3" t="n">
-        <v>0.188929</v>
+        <v>0.197023</v>
       </c>
       <c r="C106" s="3" t="n">
-        <v>-0.465484</v>
+        <v>-0.457552</v>
       </c>
       <c r="D106" s="3" t="n">
         <v>-0.112463</v>
@@ -6725,16 +6725,16 @@
         <v>-0.530369</v>
       </c>
       <c r="F106" s="3" t="n">
-        <v>-0.006739</v>
+        <v>-0.004361</v>
       </c>
       <c r="G106" s="3" t="n">
-        <v>-0.005723</v>
+        <v>-0.004143</v>
       </c>
       <c r="H106" s="3" t="n">
-        <v>0.000163</v>
+        <v>0.000141</v>
       </c>
       <c r="I106" s="3" t="n">
-        <v>0.00084</v>
+        <v>0.000447</v>
       </c>
       <c r="J106" s="3" t="n">
         <v>-0.001536</v>
@@ -8350,7 +8350,7 @@
         <v>0.09204900000000001</v>
       </c>
       <c r="K133" s="3" t="n">
-        <v>0.005748</v>
+        <v>0.436923</v>
       </c>
       <c r="L133" s="3" t="n">
         <v>0.401275</v>
@@ -18405,7 +18405,11 @@
           <t>Shares issued for cash</t>
         </is>
       </c>
-      <c r="D102" t="inlineStr"/>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E102" t="inlineStr">
         <is>
           <t>-</t>
@@ -20993,7 +20997,11 @@
           <t>Deferred income tax recovery</t>
         </is>
       </c>
-      <c r="D128" t="inlineStr"/>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E128" t="inlineStr">
         <is>
           <t>-</t>
@@ -22191,7 +22199,11 @@
           <t>Cash at end of the year $</t>
         </is>
       </c>
-      <c r="D140" t="inlineStr"/>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>EndCashPosition</t>
+        </is>
+      </c>
       <c r="E140" t="inlineStr">
         <is>
           <t>-</t>
@@ -23254,7 +23266,11 @@
           <t>GST recoverable</t>
         </is>
       </c>
-      <c r="D151" t="inlineStr"/>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>ChangeInReceivables</t>
+        </is>
+      </c>
       <c r="E151" t="inlineStr">
         <is>
           <t>-</t>
@@ -24771,7 +24787,11 @@
           <t>HST recoverable</t>
         </is>
       </c>
-      <c r="D166" t="inlineStr"/>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>ChangeInReceivables</t>
+        </is>
+      </c>
       <c r="E166" t="inlineStr">
         <is>
           <t>-</t>
@@ -28251,7 +28271,11 @@
           <t>Write-down of GST recoverable</t>
         </is>
       </c>
-      <c r="D200" t="inlineStr"/>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>ChangeInReceivables</t>
+        </is>
+      </c>
       <c r="E200" t="inlineStr">
         <is>
           <t>-</t>
@@ -30366,7 +30390,11 @@
           <t>GST recoverable</t>
         </is>
       </c>
-      <c r="D221" t="inlineStr"/>
+      <c r="D221" t="inlineStr">
+        <is>
+          <t>ChangeInReceivables</t>
+        </is>
+      </c>
       <c r="E221" s="5" t="n">
         <v>0.008094</v>
       </c>
